--- a/cloud_storage/system_config.xlsx
+++ b/cloud_storage/system_config.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,6 +425,54 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>admin_login</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>admin_password</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Моя компания</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trial_days</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
     </row>
